--- a/extenbooks/S604_extenbook.xlsx
+++ b/extenbooks/S604_extenbook.xlsx
@@ -4349,7 +4349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A95"/>
+  <dimension ref="A1:A94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4388,466 +4388,463 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Status:** ingested  **Year range (book):** 1948-2011</t>
+          <t>***Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Corporate Incremental Rate of Profit (IROP)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Corporate Incremental Rate of Profit (IROP)</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>## Why It Matters</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>## Why It Matters</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fig 6.7 source. iropcorpnipa is the canonical extended series post-2011 (iropcorp is bounded by NMINT availability). Source: Appendix Table 6.8.II.7. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fig 6.7 source. iropcorpnipa is the canonical extended series post-2011 (iropcorp is bounded by NMINT availability). Source: Appendix Table 6.8.II.7. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>## Sources (per subseries)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>## Sources (per subseries)</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>| Subseries | Appendix Table | Variable | Source agency | Notes |</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>| Subseries | Appendix Table | Variable | Source agency | Notes |</t>
+          <t>|-----------|---------------|----------|---------------|-------|</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>|-----------|---------------|----------|---------------|-------|</t>
+          <t>| S604-A | II7 | `iropcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>| S604-A | II7 | `iropcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| S604-B | II7 | `iropcorpnipa` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>| S604-B | II7 | `iropcorpnipa` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Two nominal IROP lines per Fig 6.7 panel 1: iropcorp = Delta(GOS_corp_adj) / (IG_corpbea + Delta(INV_corp)); iropcorpnipa = Delta(GOS_corpnipa) / IG_corpbea. iropcorpnipa is the canonical extended series (no NMINT/INV dependency).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Two nominal IROP lines per Fig 6.7 panel 1: iropcorp = Delta(GOS_corp_adj) / (IG_corpbea + Delta(INV_corp)); iropcorpnipa = Delta(GOS_corpnipa) / IG_corpbea. iropcorpnipa is the canonical extended series (no NMINT/INV dependency).</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>## Year Coverage</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>## Year Coverage</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Book period: 1948-2011. Vintage-stable extension recipe in `S604_EPR.md`.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Book period: 1948-2011. Vintage-stable extension recipe in `S604_EPR.md`.</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>## Units</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>## Units</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>decimal_rate</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>## Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>## Caveats</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>* iropcorp bounded by NMINT + IRS inventory completeness; iropcorpnipa is canonical for post-2011.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>* iropcorp bounded by NMINT + IRS inventory completeness; iropcorpnipa is canonical for post-2011.</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>## Cross-references</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>`AS003`, `AS004`, `AS009`</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>`AS003`, `AS004`, `AS009`</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>## Validation Expectation</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>## Validation Expectation</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>`V03_S604_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 2.0% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4">
+    <row r="50">
+      <c r="A50" s="4">
         <f>== EPR: S604_EPR.md ===</f>
         <v/>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t># S604 — Corporate Incremental Rate of Profit (IROP) (Extension Provenance Record)</t>
+        </is>
+      </c>
+    </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t># S604 — Corporate Incremental Rate of Profit (IROP) (Extension Provenance Record)</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>**Classification:** extendable_via_component_refetch  **Tolerance for extended values:** 2.0%</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>**Classification:** extendable_via_component_refetch  **Tolerance for extended values:** 2.0%</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>## Method</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>## Method</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published S604 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published S604 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
+          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
+          <t>3. Re-run the construction formula end-to-end.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3. Re-run the construction formula end-to-end.</t>
+          <t>4. Recompute AS003 (sectoral profit rates), AS004 (KNCcorp / KGCcorp), and AS009 (KTCcorp) using the same current-vintage components. NEVER splice the published profit-rate series.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4. Recompute AS003 (sectoral profit rates), AS004 (KNCcorp / KGCcorp), and AS009 (KTCcorp) using the same current-vintage components. NEVER splice the published profit-rate series.</t>
+          <t>5. For S603 x1: freeze at last complete NMINT year — do NOT forward-fill.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5. For S603 x1: freeze at last complete NMINT year — do NOT forward-fill.</t>
+          <t>6. For S604: prefer iropcorpnipa as the canonical extended series; iropcorp is bounded by NMINT / IRS-inventory availability.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>6. For S604: prefer iropcorpnipa as the canonical extended series; iropcorp is bounded by NMINT / IRS-inventory availability.</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>## Worked Example</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>## Worked Example</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>For S604, the Phase 5 round-trip validation reads `S604_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1948-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>For S604, the Phase 5 round-trip validation reads `S604_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1948-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>## No-Proxy Disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>## No-Proxy Disclosure</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>## No-Synthetic Disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>## No-Synthetic Disclosure</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>## Failure Mode Table</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>## Failure Mode Table</t>
-        </is>
-      </c>
+      <c r="A79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>| Failure | Detection | Response |</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Response |</t>
+          <t>|---------|-----------|----------|</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>|---------|-----------|----------|</t>
+          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+          <t>| FISIM T7.11 line revision (AS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>| FISIM T7.11 line revision (AS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+          <t>| BEA 1993 depreciation rate not available post-2011 | AS004/AS006/AS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | AS004/AS006/AS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
-        </is>
-      </c>
+      <c r="A87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>## CD2 Divergence Pre-Disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
-        </is>
-      </c>
+      <c r="A91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>## Anti-Degradation Compliance</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>## Anti-Degradation Compliance</t>
-        </is>
-      </c>
+      <c r="A93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
         </is>
@@ -5176,11 +5173,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5203,76 +5200,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Corporate Incremental Rate of Profit (IROP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S604_research.json", "adequacy_report": "Technical/docs/chapters/CH6_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S604_DPR.md", "epr": "Technical/docs/series/S604_EPR.md", "loader": "Technical/code/L01_loaders/L01_S604_load.py", "processor": "Technical/code/P02_processors/P02_S604_construct.py", "validator": "Technical/code/V03_validators/V03_S604_validate.py", "processed": "Technical/data/processed/S604.parquet", "chopped_csv": "Technical/chopped/S604.csv", "extenbook_xlsx": "Technical/extenbooks/S604_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:43:17.420354+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S604_extenbook.xlsx
+++ b/extenbooks/S604_extenbook.xlsx
@@ -236,6 +236,70 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Data'!D3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$A$4:$A$67</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$4:$D$67</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Data'!E3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$A$4:$A$67</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$E$4:$E$67</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -305,7 +369,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -617,14 +681,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E200"/>
+  <dimension ref="A1:E328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="57" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -651,6 +715,16 @@
           <t>S604-B</t>
         </is>
       </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -662,6 +736,12 @@
       <c r="C4" t="n">
         <v>0.7166666666666668</v>
       </c>
+      <c r="D4" t="n">
+        <v>0.3146845373281579</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.341297461611671</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -673,6 +753,12 @@
       <c r="C5" t="n">
         <v>-0.07643312101910847</v>
       </c>
+      <c r="D5" t="n">
+        <v>-0.1193329142047778</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.1300334573020225</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -684,6 +770,12 @@
       <c r="C6" t="n">
         <v>0.4269662921348315</v>
       </c>
+      <c r="D6" t="n">
+        <v>0.439186432024865</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4004315508535092</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -695,6 +787,12 @@
       <c r="C7" t="n">
         <v>0.3888888888888892</v>
       </c>
+      <c r="D7" t="n">
+        <v>0.07423948026439547</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.08489271268057841</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -706,6 +804,12 @@
       <c r="C8" t="n">
         <v>-0.0674157303370788</v>
       </c>
+      <c r="D8" t="n">
+        <v>-0.08652761196412544</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.1041707720076025</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -717,6 +821,12 @@
       <c r="C9" t="n">
         <v>0.05529953917050671</v>
       </c>
+      <c r="D9" t="n">
+        <v>0.01669263639508197</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01167770212517622</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -728,6 +838,12 @@
       <c r="C10" t="n">
         <v>-0.004405286343612398</v>
       </c>
+      <c r="D10" t="n">
+        <v>-0.01329679665649402</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.01693748038634573</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -739,6 +855,12 @@
       <c r="C11" t="n">
         <v>0.4475806451612906</v>
       </c>
+      <c r="D11" t="n">
+        <v>0.4683115288190787</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.4306074608756598</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -750,6 +872,12 @@
       <c r="C12" t="n">
         <v>0.02904564315352709</v>
       </c>
+      <c r="D12" t="n">
+        <v>-0.1179289101561938</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.1468235494679134</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -761,6 +889,12 @@
       <c r="C13" t="n">
         <v>0.0526315789473681</v>
       </c>
+      <c r="D13" t="n">
+        <v>-0.04495625858589183</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.0657126578202028</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -772,6 +906,12 @@
       <c r="C14" t="n">
         <v>-0.09937888198757772</v>
       </c>
+      <c r="D14" t="n">
+        <v>-0.09843976824313573</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.1092680892673635</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -783,6 +923,12 @@
       <c r="C15" t="n">
         <v>0.349570200573066</v>
       </c>
+      <c r="D15" t="n">
+        <v>0.3213454719068297</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.3467106106019984</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -794,6 +940,12 @@
       <c r="C16" t="n">
         <v>-0.02649006622516547</v>
       </c>
+      <c r="D16" t="n">
+        <v>-0.005165949114381718</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.02445952758078847</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,6 +957,12 @@
       <c r="C17" t="n">
         <v>0.04892966360856251</v>
       </c>
+      <c r="D17" t="n">
+        <v>0.06979668790343385</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.05284946428373647</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -816,6 +974,12 @@
       <c r="C18" t="n">
         <v>0.2415730337078654</v>
       </c>
+      <c r="D18" t="n">
+        <v>0.2458098044092056</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.2495935488628589</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -827,6 +991,12 @@
       <c r="C19" t="n">
         <v>0.1931818181818181</v>
       </c>
+      <c r="D19" t="n">
+        <v>0.1685280262198506</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1736846342161273</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -838,6 +1008,12 @@
       <c r="C20" t="n">
         <v>0.216710182767624</v>
       </c>
+      <c r="D20" t="n">
+        <v>0.18526608515762</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1898017824691055</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -849,6 +1025,12 @@
       <c r="C21" t="n">
         <v>0.3217821782178218</v>
       </c>
+      <c r="D21" t="n">
+        <v>0.257787573744619</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.258496046154695</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -860,6 +1042,12 @@
       <c r="C22" t="n">
         <v>0.1995661605206074</v>
       </c>
+      <c r="D22" t="n">
+        <v>0.1330682861076214</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.1375527519845067</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -871,6 +1059,12 @@
       <c r="C23" t="n">
         <v>0.01451905626134322</v>
       </c>
+      <c r="D23" t="n">
+        <v>-0.002242470632261009</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.0299872835747515</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -882,6 +1076,12 @@
       <c r="C24" t="n">
         <v>0.1567398119122257</v>
       </c>
+      <c r="D24" t="n">
+        <v>0.1036734759554693</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.08892613886490411</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -893,6 +1093,12 @@
       <c r="C25" t="n">
         <v>0.01232665639445318</v>
       </c>
+      <c r="D25" t="n">
+        <v>-0.009082971339768335</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.05987187499650937</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -904,6 +1110,12 @@
       <c r="C26" t="n">
         <v>-0.1070422535211271</v>
       </c>
+      <c r="D26" t="n">
+        <v>-0.1106014559446752</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.1669864796319741</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -915,6 +1127,12 @@
       <c r="C27" t="n">
         <v>0.2222222222222222</v>
       </c>
+      <c r="D27" t="n">
+        <v>0.1310239390940836</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.1405523559130199</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -926,6 +1144,12 @@
       <c r="C28" t="n">
         <v>0.2285012285012284</v>
       </c>
+      <c r="D28" t="n">
+        <v>0.168096357736103</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.162375592384216</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -937,6 +1161,12 @@
       <c r="C29" t="n">
         <v>0.1761229314420805</v>
       </c>
+      <c r="D29" t="n">
+        <v>0.1070033704367609</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.08279173469629297</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -948,6 +1178,12 @@
       <c r="C30" t="n">
         <v>0</v>
       </c>
+      <c r="D30" t="n">
+        <v>-0.07667143614407788</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.1398393243311935</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -959,6 +1195,12 @@
       <c r="C31" t="n">
         <v>0.3188153310104527</v>
       </c>
+      <c r="D31" t="n">
+        <v>0.05120665827171766</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.08372438810151077</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -970,6 +1212,12 @@
       <c r="C32" t="n">
         <v>0.2789634146341465</v>
       </c>
+      <c r="D32" t="n">
+        <v>0.1788507473506982</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.1729905817600822</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -981,6 +1229,12 @@
       <c r="C33" t="n">
         <v>0.3059701492537309</v>
       </c>
+      <c r="D33" t="n">
+        <v>0.134696972032776</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.155603512085304</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -992,6 +1246,12 @@
       <c r="C34" t="n">
         <v>0.2637954239569317</v>
       </c>
+      <c r="D34" t="n">
+        <v>0.1313083260557697</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.1134925218102104</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1003,6 +1263,12 @@
       <c r="C35" t="n">
         <v>0.09019165727170236</v>
       </c>
+      <c r="D35" t="n">
+        <v>0.001155553498735689</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.04273367429620755</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1014,6 +1280,12 @@
       <c r="C36" t="n">
         <v>0</v>
       </c>
+      <c r="D36" t="n">
+        <v>-0.05769377375211508</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.103696642507401</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1025,6 +1297,12 @@
       <c r="C37" t="n">
         <v>0.2154142581888246</v>
       </c>
+      <c r="D37" t="n">
+        <v>0.1101630586613128</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.07359259610684279</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1036,6 +1314,12 @@
       <c r="C38" t="n">
         <v>0.009838369641602288</v>
       </c>
+      <c r="D38" t="n">
+        <v>-0.03341401311443026</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.05581746748033558</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1047,6 +1331,12 @@
       <c r="C39" t="n">
         <v>0.187422934648582</v>
       </c>
+      <c r="D39" t="n">
+        <v>0.2066641506687716</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.2016469558101208</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1058,6 +1348,12 @@
       <c r="C40" t="n">
         <v>0.2130846835830023</v>
       </c>
+      <c r="D40" t="n">
+        <v>0.2570833910827757</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.2236145128748612</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1069,6 +1365,12 @@
       <c r="C41" t="n">
         <v>0.0963855421686745</v>
       </c>
+      <c r="D41" t="n">
+        <v>0.08261377556187442</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.0762560762187405</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1080,6 +1382,12 @@
       <c r="C42" t="n">
         <v>-0.004171011470281602</v>
       </c>
+      <c r="D42" t="n">
+        <v>-0.003122592822101191</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.0165800046781539</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1091,6 +1399,12 @@
       <c r="C43" t="n">
         <v>0.1495757575757577</v>
       </c>
+      <c r="D43" t="n">
+        <v>0.1324324364308569</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.1442609621921399</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1102,6 +1416,12 @@
       <c r="C44" t="n">
         <v>0.1794680586626896</v>
       </c>
+      <c r="D44" t="n">
+        <v>0.1332554209737923</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.1382927396095341</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1113,6 +1433,12 @@
       <c r="C45" t="n">
         <v>0.02677907265063217</v>
       </c>
+      <c r="D45" t="n">
+        <v>0.06974879910377059</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-0.005396095941438379</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1124,6 +1450,12 @@
       <c r="C46" t="n">
         <v>0.05147737765466287</v>
       </c>
+      <c r="D46" t="n">
+        <v>0.02454390458660318</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.02235064572530931</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1135,6 +1467,12 @@
       <c r="C47" t="n">
         <v>0.08780487804878068</v>
       </c>
+      <c r="D47" t="n">
+        <v>0.0370140242977081</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.06341642095995922</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1146,6 +1484,12 @@
       <c r="C48" t="n">
         <v>0.1039633539135631</v>
       </c>
+      <c r="D48" t="n">
+        <v>0.07499077658227603</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.1253592838567411</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1157,6 +1501,12 @@
       <c r="C49" t="n">
         <v>0.1281094527363183</v>
       </c>
+      <c r="D49" t="n">
+        <v>0.09008062481490402</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.1254320192696873</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1168,6 +1518,12 @@
       <c r="C50" t="n">
         <v>0.2186553603876437</v>
       </c>
+      <c r="D50" t="n">
+        <v>0.1834304860350543</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.1923162781085034</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1179,6 +1535,12 @@
       <c r="C51" t="n">
         <v>0.1923359002566925</v>
       </c>
+      <c r="D51" t="n">
+        <v>0.1450524194274639</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.1680854591121055</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1190,6 +1552,12 @@
       <c r="C52" t="n">
         <v>0.1754619610454467</v>
       </c>
+      <c r="D52" t="n">
+        <v>0.2349682557005037</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.1854516209467192</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1201,6 +1569,12 @@
       <c r="C53" t="n">
         <v>0.1670124481327802</v>
       </c>
+      <c r="D53" t="n">
+        <v>0.1764878588973229</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.184096592622244</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1212,6 +1586,12 @@
       <c r="C54" t="n">
         <v>-0.04107725788900955</v>
       </c>
+      <c r="D54" t="n">
+        <v>0.06069968904756862</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.005104506344024613</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1223,6 +1603,12 @@
       <c r="C55" t="n">
         <v>0.08924999999999955</v>
       </c>
+      <c r="D55" t="n">
+        <v>0.1225433716858866</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.1066096873654934</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1234,6 +1620,12 @@
       <c r="C56" t="n">
         <v>-0.004592422502870003</v>
       </c>
+      <c r="D56" t="n">
+        <v>0.04926210833552673</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.003265247229609497</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1245,6 +1637,12 @@
       <c r="C57" t="n">
         <v>-0.01701363204057924</v>
       </c>
+      <c r="D57" t="n">
+        <v>0.008170456653117567</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-0.009773993148534395</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1256,6 +1654,12 @@
       <c r="C58" t="n">
         <v>0.1194835228367701</v>
       </c>
+      <c r="D58" t="n">
+        <v>0.07722045403327409</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.1313546098377349</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1267,6 +1671,12 @@
       <c r="C59" t="n">
         <v>0.1176767167490169</v>
       </c>
+      <c r="D59" t="n">
+        <v>0.09976838279811491</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.1355018626968877</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1278,6 +1688,12 @@
       <c r="C60" t="n">
         <v>0.299062252852785</v>
       </c>
+      <c r="D60" t="n">
+        <v>0.2339943861598235</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.2732286575758339</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1289,6 +1705,12 @@
       <c r="C61" t="n">
         <v>0.2549899080511321</v>
       </c>
+      <c r="D61" t="n">
+        <v>0.1660240209501685</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.1766808375462107</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1300,6 +1722,12 @@
       <c r="C62" t="n">
         <v>0.2057291666666671</v>
       </c>
+      <c r="D62" t="n">
+        <v>0.09608433635981628</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.1115348518048242</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1311,6 +1739,12 @@
       <c r="C63" t="n">
         <v>-0.125516334960571</v>
       </c>
+      <c r="D63" t="n">
+        <v>-0.07428632023290407</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.148342806387135</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1322,6 +1756,12 @@
       <c r="C64" t="n">
         <v>-0.2228834870075439</v>
       </c>
+      <c r="D64" t="n">
+        <v>-0.1932362501238226</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-0.2352928365707835</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1333,6 +1773,12 @@
       <c r="C65" t="n">
         <v>0.1154944800432333</v>
       </c>
+      <c r="D65" t="n">
+        <v>0.1303451452797239</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.1350260102817996</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1344,6 +1790,12 @@
       <c r="C66" t="n">
         <v>0.2344643537933664</v>
       </c>
+      <c r="D66" t="n">
+        <v>0.3415192800486044</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.3041547041383983</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1354,6 +1806,12 @@
       </c>
       <c r="C67" t="n">
         <v>0.1167841493617831</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.08080588131264715</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.06888604578238343</v>
       </c>
     </row>
     <row r="68"/>
@@ -4332,6 +4790,2950 @@
         </is>
       </c>
       <c r="E200" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>1948</v>
+      </c>
+      <c r="B201" t="n">
+        <v>0.3146845373281579</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>1949</v>
+      </c>
+      <c r="B202" t="n">
+        <v>-0.1193329142047778</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>1950</v>
+      </c>
+      <c r="B203" t="n">
+        <v>0.439186432024865</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>1951</v>
+      </c>
+      <c r="B204" t="n">
+        <v>0.07423948026439547</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>1952</v>
+      </c>
+      <c r="B205" t="n">
+        <v>-0.08652761196412544</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>1953</v>
+      </c>
+      <c r="B206" t="n">
+        <v>0.01669263639508197</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>1954</v>
+      </c>
+      <c r="B207" t="n">
+        <v>-0.01329679665649402</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>1955</v>
+      </c>
+      <c r="B208" t="n">
+        <v>0.4683115288190787</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>1956</v>
+      </c>
+      <c r="B209" t="n">
+        <v>-0.1179289101561938</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>1957</v>
+      </c>
+      <c r="B210" t="n">
+        <v>-0.04495625858589183</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>1958</v>
+      </c>
+      <c r="B211" t="n">
+        <v>-0.09843976824313573</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>1959</v>
+      </c>
+      <c r="B212" t="n">
+        <v>0.3213454719068297</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B213" t="n">
+        <v>-0.005165949114381718</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B214" t="n">
+        <v>0.06979668790343385</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B215" t="n">
+        <v>0.2458098044092056</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B216" t="n">
+        <v>0.1685280262198506</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B217" t="n">
+        <v>0.18526608515762</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B218" t="n">
+        <v>0.257787573744619</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B219" t="n">
+        <v>0.1330682861076214</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B220" t="n">
+        <v>-0.002242470632261009</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B221" t="n">
+        <v>0.1036734759554693</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B222" t="n">
+        <v>-0.009082971339768335</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B223" t="n">
+        <v>-0.1106014559446752</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B224" t="n">
+        <v>0.1310239390940836</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B225" t="n">
+        <v>0.168096357736103</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B226" t="n">
+        <v>0.1070033704367609</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B227" t="n">
+        <v>-0.07667143614407788</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B228" t="n">
+        <v>0.05120665827171766</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B229" t="n">
+        <v>0.1788507473506982</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B230" t="n">
+        <v>0.134696972032776</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B231" t="n">
+        <v>0.1313083260557697</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B232" t="n">
+        <v>0.001155553498735689</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B233" t="n">
+        <v>-0.05769377375211508</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B234" t="n">
+        <v>0.1101630586613128</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B235" t="n">
+        <v>-0.03341401311443026</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B236" t="n">
+        <v>0.2066641506687716</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B237" t="n">
+        <v>0.2570833910827757</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B238" t="n">
+        <v>0.08261377556187442</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B239" t="n">
+        <v>-0.003122592822101191</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B240" t="n">
+        <v>0.1324324364308569</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B241" t="n">
+        <v>0.1332554209737923</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B242" t="n">
+        <v>0.06974879910377059</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B243" t="n">
+        <v>0.02454390458660318</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B244" t="n">
+        <v>0.0370140242977081</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B245" t="n">
+        <v>0.07499077658227603</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B246" t="n">
+        <v>0.09008062481490402</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B247" t="n">
+        <v>0.1834304860350543</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B248" t="n">
+        <v>0.1450524194274639</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B249" t="n">
+        <v>0.2349682557005037</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B250" t="n">
+        <v>0.1764878588973229</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B251" t="n">
+        <v>0.06069968904756862</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B252" t="n">
+        <v>0.1225433716858866</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B253" t="n">
+        <v>0.04926210833552673</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B254" t="n">
+        <v>0.008170456653117567</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B255" t="n">
+        <v>0.07722045403327409</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B256" t="n">
+        <v>0.09976838279811491</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B257" t="n">
+        <v>0.2339943861598235</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B258" t="n">
+        <v>0.1660240209501685</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B259" t="n">
+        <v>0.09608433635981628</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B260" t="n">
+        <v>-0.07428632023290407</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B261" t="n">
+        <v>-0.1932362501238226</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B262" t="n">
+        <v>0.1303451452797239</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B263" t="n">
+        <v>0.3415192800486044</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B264" t="n">
+        <v>0.08080588131264715</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>1948</v>
+      </c>
+      <c r="B265" t="n">
+        <v>0.341297461611671</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>1949</v>
+      </c>
+      <c r="B266" t="n">
+        <v>-0.1300334573020225</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>1950</v>
+      </c>
+      <c r="B267" t="n">
+        <v>0.4004315508535092</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>1951</v>
+      </c>
+      <c r="B268" t="n">
+        <v>0.08489271268057841</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>1952</v>
+      </c>
+      <c r="B269" t="n">
+        <v>-0.1041707720076025</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>1953</v>
+      </c>
+      <c r="B270" t="n">
+        <v>0.01167770212517622</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>1954</v>
+      </c>
+      <c r="B271" t="n">
+        <v>-0.01693748038634573</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>1955</v>
+      </c>
+      <c r="B272" t="n">
+        <v>0.4306074608756598</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>1956</v>
+      </c>
+      <c r="B273" t="n">
+        <v>-0.1468235494679134</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>1957</v>
+      </c>
+      <c r="B274" t="n">
+        <v>-0.0657126578202028</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>1958</v>
+      </c>
+      <c r="B275" t="n">
+        <v>-0.1092680892673635</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>1959</v>
+      </c>
+      <c r="B276" t="n">
+        <v>0.3467106106019984</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B277" t="n">
+        <v>-0.02445952758078847</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B278" t="n">
+        <v>0.05284946428373647</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B279" t="n">
+        <v>0.2495935488628589</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B280" t="n">
+        <v>0.1736846342161273</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B281" t="n">
+        <v>0.1898017824691055</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B282" t="n">
+        <v>0.258496046154695</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B283" t="n">
+        <v>0.1375527519845067</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B284" t="n">
+        <v>-0.0299872835747515</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B285" t="n">
+        <v>0.08892613886490411</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B286" t="n">
+        <v>-0.05987187499650937</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B287" t="n">
+        <v>-0.1669864796319741</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B288" t="n">
+        <v>0.1405523559130199</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B289" t="n">
+        <v>0.162375592384216</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B290" t="n">
+        <v>0.08279173469629297</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B291" t="n">
+        <v>-0.1398393243311935</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B292" t="n">
+        <v>0.08372438810151077</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B293" t="n">
+        <v>0.1729905817600822</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B294" t="n">
+        <v>0.155603512085304</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B295" t="n">
+        <v>0.1134925218102104</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B296" t="n">
+        <v>-0.04273367429620755</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B297" t="n">
+        <v>-0.103696642507401</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B298" t="n">
+        <v>0.07359259610684279</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B299" t="n">
+        <v>-0.05581746748033558</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B300" t="n">
+        <v>0.2016469558101208</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B301" t="n">
+        <v>0.2236145128748612</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B302" t="n">
+        <v>0.0762560762187405</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B303" t="n">
+        <v>-0.0165800046781539</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B304" t="n">
+        <v>0.1442609621921399</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B305" t="n">
+        <v>0.1382927396095341</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B306" t="n">
+        <v>-0.005396095941438379</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B307" t="n">
+        <v>0.02235064572530931</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B308" t="n">
+        <v>0.06341642095995922</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B309" t="n">
+        <v>0.1253592838567411</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B310" t="n">
+        <v>0.1254320192696873</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B311" t="n">
+        <v>0.1923162781085034</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B312" t="n">
+        <v>0.1680854591121055</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B313" t="n">
+        <v>0.1854516209467192</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B314" t="n">
+        <v>0.184096592622244</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B315" t="n">
+        <v>0.005104506344024613</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B316" t="n">
+        <v>0.1066096873654934</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B317" t="n">
+        <v>-0.003265247229609497</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B318" t="n">
+        <v>-0.009773993148534395</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B319" t="n">
+        <v>0.1313546098377349</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B320" t="n">
+        <v>0.1355018626968877</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B321" t="n">
+        <v>0.2732286575758339</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B322" t="n">
+        <v>0.1766808375462107</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B323" t="n">
+        <v>0.1115348518048242</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B324" t="n">
+        <v>-0.148342806387135</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B325" t="n">
+        <v>-0.2352928365707835</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B326" t="n">
+        <v>0.1350260102817996</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B327" t="n">
+        <v>0.3041547041383983</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B328" t="n">
+        <v>0.06888604578238343</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>SHAIKH_APP_6_8_II7</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
         <is>
           <t>decimal_rate</t>
         </is>
@@ -4349,7 +7751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A94"/>
+  <dimension ref="A1:A122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4405,7 +7807,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Corporate Incremental Rate of Profit (IROP)</t>
+          <t>Corporate Incremental Rate of Profit — the incremental rate of profit (IROP), i.e. the return on newly added capital: the year-to-year change in profit divided by the new investment that produced it (as distinct from the *average* rate of profit on the whole existing capital stock).</t>
         </is>
       </c>
     </row>
@@ -4425,7 +7827,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fig 6.7 source. iropcorpnipa is the canonical extended series post-2011 (iropcorp is bounded by NMINT availability). Source: Appendix Table 6.8.II.7. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+          <t>Source figure: Fig 6.7, which has two panels — a nominal panel and a current-cost ("real") panel — and whose four averages are printed in Table 6.24. All four lines are shipped: two nominal (iropcorp, iropcorpnipa) and two current-cost (iroprcorp, iroprcorpnipa). Within each pair, the NIPA-based line (iropcorpnipa / iroprcorpnipa) is the one preferred for extension past 2011, because it has no dependence on net monetary interest (NMINT) or inventory data, which run short. The book-period values are transcribed verbatim from Shaikh's published Appendix 6.8 (sub-table II.7). See `CH6_GPIM_SUMMARY.md` for the full Chapter 6 construction pipeline.</t>
         </is>
       </c>
     </row>
@@ -4459,24 +7861,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>| S604-A | II7 | `iropcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| S604-A | II7 | `iropcorp` | BEA NIPA / BEA FA / IRS SOI / Census | nominal, corrected |</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>| S604-B | II7 | `iropcorpnipa` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| S604-B | II7 | `iropcorpnipa` | BEA NIPA / BEA FA / IRS SOI / Census | nominal, NIPA |</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>| S604-C | II7 | `iroprcorp` | BEA NIPA / BEA FA / IRS SOI / Census | current-cost ("real"), corrected |</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
+          <t>| S604-D | II7 | `iroprcorpnipa` | BEA NIPA / BEA FA / IRS SOI / Census | current-cost ("real"), NIPA |</t>
         </is>
       </c>
     </row>
@@ -4486,7 +7892,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
         </is>
       </c>
     </row>
@@ -4496,7 +7902,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Two nominal IROP lines per Fig 6.7 panel 1: iropcorp = Delta(GOS_corp_adj) / (IG_corpbea + Delta(INV_corp)); iropcorpnipa = Delta(GOS_corpnipa) / IG_corpbea. iropcorpnipa is the canonical extended series (no NMINT/INV dependency).</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -4506,7 +7912,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>## Year Coverage</t>
+          <t>Four incremental-profit-rate lines across the two panels of Fig 6.7. The two nominal lines (panel 1) are iropcorp = Δ(GOS_corp_adj) / (IG_corpbea + Δ(INV_corp)) and iropcorpnipa = Δ(GOS_corpnipa) / IG_corpbea, where Δ is the year-to-year change, GOS is gross operating surplus, IG is gross investment, and INV is inventories. The two current-cost ("real") lines (panel 2) are the same ratios computed on current-cost-valued surplus and capital (iroprcorp, iroprcorpnipa). Within each pair the NIPA line (iropcorpnipa / iroprcorpnipa) is preferred for extension because it carries no net-monetary-interest or inventory dependency. All four are transcribed verbatim from Appendix 6.8 for the book period; the linked components XS003 / XS004 / XS009 (appendix "extra series" holding the GPIM internals) are recorded as **documentary lineage** per Decision 0015, not a live computation wired into this package.</t>
         </is>
       </c>
     </row>
@@ -4516,7 +7922,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Book period: 1948-2011. Vintage-stable extension recipe in `S604_EPR.md`.</t>
+          <t>## Year Coverage</t>
         </is>
       </c>
     </row>
@@ -4526,7 +7932,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>## Units</t>
+          <t>Book period: 1948-2011. Vintage-stable extension recipe in `S604_EPR.md`.</t>
         </is>
       </c>
     </row>
@@ -4536,7 +7942,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>decimal_rate</t>
+          <t>## Units</t>
         </is>
       </c>
     </row>
@@ -4546,7 +7952,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>## Caveats</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4556,7 +7962,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>* iropcorp bounded by NMINT + IRS inventory completeness; iropcorpnipa is canonical for post-2011.</t>
+          <t>## Caveats</t>
         </is>
       </c>
     </row>
@@ -4566,7 +7972,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>## Cross-references</t>
+          <t>* The corrected lines (iropcorp, iroprcorp) are bounded by net-monetary-interest (NMINT) and IRS inventory completeness; the NIPA lines (iropcorpnipa, iroprcorpnipa) are the ones carried forward for post-2011 extension.</t>
         </is>
       </c>
     </row>
@@ -4576,7 +7982,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>`AS003`, `AS004`, `AS009`</t>
+          <t>## Cross-references</t>
         </is>
       </c>
     </row>
@@ -4586,7 +7992,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>## Validation Expectation</t>
+          <t>`XS003`, `XS004`, `XS009`</t>
         </is>
       </c>
     </row>
@@ -4596,217 +8002,221 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>`V03_S604_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 2.0% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
+          <t>## Validation Expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>`V03_S604` (the validate script) round-trip-checks the built series against the Appendix 6.8 source workbook at 2.0% tolerance. Table 6.24's printed averages give a non-circular anchor for the four lines' means. Per the readiness (adequacy) review (`CH6_ADEQUACY_REPORT.json`), the two ingestion blockers B2 (a National Income and Product Accounts table 7.11 FISIM re-mapping, handled by `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4">
+      <c r="A50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>- **IROP / incremental rate of profit** — the return on newly added capital: the year-to-year change in profit divided by the new investment that produced it (contrast with the *average* rate of profit on the whole existing capital stock).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>- **Subseries (S604-A … -D)** — the four data lines that make up series S604 (two nominal, two current-cost); each suffix letter is one curve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>- **GOS / IG / INV** — gross operating surplus / gross investment / inventories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>- **GPIM** — the corrected capital-stock-and-surplus construction Shaikh uses across Chapter 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>- **NMINT** — net monetary interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>- **NIPA / BEA / FA** — US National Income and Product Accounts / Bureau of Economic Analysis / its Fixed Asset accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>- **XS003 / XS004 / XS009** — appendix "extra series" recording GPIM construction internals; documentary lineage, not a live computation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>- **L01 / P02 / V03** — the load / process / validate scripts that build and check the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset, retained for cross-checking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4">
         <f>== EPR: S604_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t># S604 — Corporate Incremental Rate of Profit (IROP) (Extension Provenance Record)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>**Classification:** extendable_via_component_refetch  **Tolerance for extended values:** 2.0%</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>## Method</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published S604 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published S604 values**. Instead, the extension re-fetches the underlying US national-accounts components (BEA National Income and Product Accounts / Fixed Asset accounts, IRS, Census) and re-runs the formula end-to-end at the current vintage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>&gt; **Scope note (Decision 0015).** The shipped data covers the book period only, transcribed verbatim from Shaikh's Appendix 6.8; the linked components XS003 / XS004 / XS009 are recorded as **documentary lineage**, not a live computation wired into this package. The component-refetch-and-recompute recipe below is the *designed forward extension* method; live GPIM re-computation is on the roadmap (Phase L) and has not yet been executed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
         </is>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>3. Re-run the construction formula end-to-end.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>4. Recompute AS003 (sectoral profit rates), AS004 (KNCcorp / KGCcorp), and AS009 (KTCcorp) using the same current-vintage components. NEVER splice the published profit-rate series.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>5. For S603 x1: freeze at last complete NMINT year — do NOT forward-fill.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>6. For S604: prefer iropcorpnipa as the canonical extended series; iropcorp is bounded by NMINT / IRS-inventory availability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>## Worked Example</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>For S604, the Phase 5 round-trip validation reads `S604_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1948-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>## No-Proxy Disclosure</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>## No-Synthetic Disclosure</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>3. Re-run the construction formula end-to-end.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>## Failure Mode Table</t>
+          <t>4. Recompute XS003 (sectoral profit rates), XS004 (KNCcorp / KGCcorp), and XS009 (KTCcorp) using the same current-vintage components. NEVER splice the published profit-rate series.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>5. For S603 x1: freeze at last complete NMINT year — do NOT forward-fill.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Response |</t>
+          <t>6. For S604: prefer iropcorpnipa as the canonical extended series; iropcorp is bounded by NMINT / IRS-inventory availability.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>|---------|-----------|----------|</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+          <t>## Worked Example</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
-        </is>
-      </c>
+      <c r="A83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+          <t>For S604, the Phase 5 round-trip validation reads `S604_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1948-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>| FISIM T7.11 line revision (AS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
-        </is>
-      </c>
+      <c r="A85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | AS004/AS006/AS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
+          <t>## No-Proxy Disclosure</t>
         </is>
       </c>
     </row>
@@ -4816,7 +8226,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
+          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
         </is>
       </c>
     </row>
@@ -4826,7 +8236,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
+          <t>## No-Synthetic Disclosure</t>
         </is>
       </c>
     </row>
@@ -4836,7 +8246,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>## Anti-Degradation Compliance</t>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
         </is>
       </c>
     </row>
@@ -4846,7 +8256,175 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
+          <t>## Failure Mode Table</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>| Failure | Detection | Response |</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>|---------|-----------|----------|</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>| FISIM T7.11 line revision (XS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>## CD2 Divergence Pre-Disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>## Anti-Degradation Compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Per the Anu Framework anti-degradation rule, the *designed* extension re-fetches the BEA / IRS / FRB component series and re-computes the formula end-to-end; splicing the published series is FORBIDDEN. (Book-period data ships as the verbatim Appendix 6.8 transcription; the recompute is the roadmap Phase L method — see the Scope note above.) The loader caches BEA / FRED responses with a 30-day time-to-live (book-period values are cached permanently).</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>- **IROP / incremental rate of profit** — the return on newly added capital: the year-to-year change in profit divided by the new investment that produced it (contrast with the *average* rate of profit on the whole existing capital stock).</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>- **GPIM** — the corrected capital-stock-and-surplus construction Shaikh uses across Chapter 6 (his integrated measure of the profit rate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>- **NMINT** — net monetary interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>- **NIPA / BEA / FA / IRS / FRB** — US National Income and Product Accounts / Bureau of Economic Analysis / its Fixed Asset accounts / Internal Revenue Service / Federal Reserve Board.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>- **FISIM** — financial intermediation services indirectly measured (a national-accounts imputation affecting the T7.11 interest line).</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>- **XS003 / XS004 / XS009** — appendix "extra series" recording GPIM construction internals; documentary lineage, not a live computation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>- **L01 / V03** — the load and validate scripts that build and check the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset, retained for cross-checking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>- **Phase 5 / Phase L** — Anu pipeline stages: Phase 5 = ingestion (the shipped book-period build); Phase L = the roadmap live-recompute extension stage.</t>
         </is>
       </c>
     </row>
@@ -4861,7 +8439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5016,6 +8594,100 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>S604-C</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_6_8</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Shaikh, Capitalism (2016) — Appendix 6.8 Tables I.1-3 and II.1-7 (NIPA decomposition, GPIM capital stock, sectoral profit rates).</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Anwar Shaikh (author construction; underlying data BEA + IRS + Census + FRB)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>http://www.anwarshaikhecon.org/ (live DNS fails 2026-05-18; Wayback snapshot reachable)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>billions of current USD; depreciation rates in decimals; profit rates and ratios dimensionless</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>annual (1925-2011 for capital stock; 1947-2011 for NOS/profit)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Copyright Oxford University Press; reproduced under fair use for research</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>verbatim from Shaikh's posted Excel workbooks (SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S604-D</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_6_8</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Shaikh, Capitalism (2016) — Appendix 6.8 Tables I.1-3 and II.1-7 (NIPA decomposition, GPIM capital stock, sectoral profit rates).</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Anwar Shaikh (author construction; underlying data BEA + IRS + Census + FRB)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>http://www.anwarshaikhecon.org/ (live DNS fails 2026-05-18; Wayback snapshot reachable)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>billions of current USD; depreciation rates in decimals; profit rates and ratios dimensionless</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>annual (1925-2011 for capital stock; 1947-2011 for NOS/profit)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Copyright Oxford University Press; reproduced under fair use for research</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>verbatim from Shaikh's posted Excel workbooks (SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5027,11 +8699,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5083,7 +8755,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7">
@@ -5146,19 +8818,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>["S604-A", "S604-B"]</t>
+          <t>["S604-A", "S604-B", "S604-C", "S604-D"]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>anchor_checks</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{"verdict": "PASS", "independent_anchors": {"status": "GREEN", "sid": "S604", "n_anchors": 4, "n_red": 0, "n_green": 4, "n_na": 0, "anchors": [{"anchor_id": "S604_T624_mean_A", "anchor_type": "derived_statistic", "subseries_id": "S604-A", "source_description": "Table 6.24 (book p.256): per-period mean of iropcorp = 13.45% (decimal 0.1345). Genuine non-circular anchor (CH06_review non_circular_book_anchors).", "status": "GREEN", "expected": 0.1345, "actual": 0.13447268, "abs_pct_diff": 0.020311, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S604_T624_mean_B", "anchor_type": "derived_statistic", "subseries_id": "S604-B", "source_description": "Table 6.24 (book p.256): per-period mean of iropcorpnipa = 13.62% (decimal 0.1362).", "status": "GREEN", "expected": 0.1362, "actual": 0.13618539, "abs_pct_diff": 0.010728, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S604_T624_mean_C", "anchor_type": "derived_statistic", "subseries_id": "S604-C", "source_description": "Table 6.24 (book p.256): per-period mean of real/current-cost iroprcorp = 9.50% (decimal 0.0950). Genuine non-circular anchor (CH06_review non_circular_book_anchors; S604_MHR.md section 1).", "status": "GREEN", "expected": 0.095, "actual": 0.09501093, "abs_pct_diff": 0.011503, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S604_T624_mean_D", "anchor_type": "derived_statistic", "subseries_id": "S604-D", "source_description": "Table 6.24 (book p.256): per-period mean of real/current-cost iroprcorpnipa = 8.49% (decimal 0.0849).", "status": "GREEN", "expected": 0.0849, "actual": 0.08492683, "abs_pct_diff": 0.031604, "tolerance_pct": 1.0, "detail": "n=64"}]}, "splice_continuity": {"status": "NA", "sid": "S604", "splice_year": 2012, "detail": "no subseries spans 2011-&gt;2012"}, "level_plausibility": {"status": "NA", "sid": "S604", "n_rules": 0, "rules": [], "detail": "no plausibility_rules registered"}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>validated_at</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-18T23:03:53.965027+00:00</t>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-02T06:24:56.481696+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S604_extenbook.xlsx
+++ b/extenbooks/S604_extenbook.xlsx
@@ -8830,7 +8830,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{"verdict": "PASS", "independent_anchors": {"status": "GREEN", "sid": "S604", "n_anchors": 4, "n_red": 0, "n_green": 4, "n_na": 0, "anchors": [{"anchor_id": "S604_T624_mean_A", "anchor_type": "derived_statistic", "subseries_id": "S604-A", "source_description": "Table 6.24 (book p.256): per-period mean of iropcorp = 13.45% (decimal 0.1345). Genuine non-circular anchor (CH06_review non_circular_book_anchors).", "status": "GREEN", "expected": 0.1345, "actual": 0.13447268, "abs_pct_diff": 0.020311, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S604_T624_mean_B", "anchor_type": "derived_statistic", "subseries_id": "S604-B", "source_description": "Table 6.24 (book p.256): per-period mean of iropcorpnipa = 13.62% (decimal 0.1362).", "status": "GREEN", "expected": 0.1362, "actual": 0.13618539, "abs_pct_diff": 0.010728, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S604_T624_mean_C", "anchor_type": "derived_statistic", "subseries_id": "S604-C", "source_description": "Table 6.24 (book p.256): per-period mean of real/current-cost iroprcorp = 9.50% (decimal 0.0950). Genuine non-circular anchor (CH06_review non_circular_book_anchors; S604_MHR.md section 1).", "status": "GREEN", "expected": 0.095, "actual": 0.09501093, "abs_pct_diff": 0.011503, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S604_T624_mean_D", "anchor_type": "derived_statistic", "subseries_id": "S604-D", "source_description": "Table 6.24 (book p.256): per-period mean of real/current-cost iroprcorpnipa = 8.49% (decimal 0.0849).", "status": "GREEN", "expected": 0.0849, "actual": 0.08492683, "abs_pct_diff": 0.031604, "tolerance_pct": 1.0, "detail": "n=64"}]}, "splice_continuity": {"status": "NA", "sid": "S604", "splice_year": 2012, "detail": "no subseries spans 2011-&gt;2012"}, "level_plausibility": {"status": "NA", "sid": "S604", "n_rules": 0, "rules": [], "detail": "no plausibility_rules registered"}}</t>
+          <t>{"verdict": "PASS", "independent_anchors": {"status": "GREEN", "sid": "S604", "n_anchors": 4, "n_red": 0, "n_green": 4, "n_na": 0, "anchors": [{"anchor_id": "S604_T624_mean_A", "anchor_type": "derived_statistic", "subseries_id": "S604-A", "source_description": "Table 6.24 (book p.256): per-period mean of iropcorp = 13.45% (decimal 0.1345). Genuine non-circular anchor (CH06_review non_circular_book_anchors).", "status": "GREEN", "expected": 0.1345, "actual": 0.13447268, "abs_pct_diff": 0.020311, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S604_T624_mean_B", "anchor_type": "derived_statistic", "subseries_id": "S604-B", "source_description": "Table 6.24 (book p.256): per-period mean of iropcorpnipa = 13.62% (decimal 0.1362).", "status": "GREEN", "expected": 0.1362, "actual": 0.13618539, "abs_pct_diff": 0.010728, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S604_T624_mean_C", "anchor_type": "derived_statistic", "subseries_id": "S604-C", "source_description": "Table 6.24 (book p.256): per-period mean of real/current-cost iroprcorp = 9.50% (decimal 0.0950). Genuine non-circular anchor (CH06_review non_circular_book_anchors; S604_MHR.md section 1).", "status": "GREEN", "expected": 0.095, "actual": 0.09501093, "abs_pct_diff": 0.011503, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S604_T624_mean_D", "anchor_type": "derived_statistic", "subseries_id": "S604-D", "source_description": "Table 6.24 (book p.256): per-period mean of real/current-cost iroprcorpnipa = 8.49% (decimal 0.0849).", "status": "GREEN", "expected": 0.0849, "actual": 0.08492683, "abs_pct_diff": 0.031604, "tolerance_pct": 1.0, "detail": "n=64"}]}, "splice_continuity": {"status": "NA", "sid": "S604", "detail": "no extension / no book+extension ranges"}, "level_plausibility": {"status": "NA", "sid": "S604", "n_rules": 0, "rules": [], "detail": "no plausibility_rules registered"}}</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-02T06:24:56.481696+00:00</t>
+          <t>2026-07-11T03:44:25.863581+00:00</t>
         </is>
       </c>
     </row>
@@ -8857,11 +8857,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8884,6 +8884,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_6_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>book_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful reconstruction of Shaikh Figure 6.7 (Ch6, nominal panel). Two incremental-profit-rate lines, 1948-2011: Shaikh's corrected measure and the simpler NIPA measure, transcribed from Shaikh's Appendix 6.8 Table II-7. Construction-relevant: the incremental rate is Shaikh's proxy for the return on new capital that governs turbulent profit-rate equalization, and the near-identity of the corrected and NIPA versions is a headline methodological finding licensing the simpler measure for cross-country work.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S604_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S604_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fig 6.7 source (both panels, four curves: nominal iropcorp/iropcorpnipa = S604-A/B; real/current-cost iroprcorp/iroprcorpnipa = S604-C/D, added 2026-07-01 remediation T1.5 closing CH06_review H1). iropcorpnipa is the canonical extended series post-2011 (iropcorp is bounded by NMINT availability). Source: Appendix Table 6.8.II.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>decimal_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
